--- a/artfynd/A 13558-2025 artfynd.xlsx
+++ b/artfynd/A 13558-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5394863</v>
+        <v>6777289</v>
       </c>
       <c r="B2" t="n">
-        <v>98979</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222929</v>
+        <v>770</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backruta</t>
+          <t>Honungsblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thalictrum simplex</t>
+          <t>Herminium monorchis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608597.0997937612</v>
+        <v>608692</v>
       </c>
       <c r="R2" t="n">
-        <v>6296642.111885821</v>
+        <v>6296653</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,21 +747,11 @@
           <t>2005-07-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-07-25</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,11 +760,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>torräng</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,7 +772,762 @@
           <t>Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2992293</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99103</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219799</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Epipactis palustris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Störlinge ost, Öl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>608692</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6296653</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gärdslösa</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2005-07-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2005-07-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>kalkfuktäng</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2303068</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Störlinge ost, Öl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>608692</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6296653</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gärdslösa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2005-07-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2005-07-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>torräng</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2457148</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108115</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Störlinge ost, Öl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>608692</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6296653</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gärdslösa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2005-07-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2005-07-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>torräng</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3366866</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106155</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Störlinge ost, Öl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>608692</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6296653</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gärdslösa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2005-07-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2005-07-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>torräng</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4797685</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99802</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Störlinge ost, Öl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>608692</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6296653</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gärdslösa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2005-07-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2005-07-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>kalkfuktäng</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5394863</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101793</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222929</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Backruta</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Thalictrum simplex</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Störlinge ost, Öl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>608597</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6296642</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gärdslösa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2005-07-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2005-07-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>torräng</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6104106</v>
+      </c>
+      <c r="B9" t="n">
+        <v>102346</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>224145</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stallört</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ononis spinosa subsp. hircina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Jacq.) Gams</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Störlinge ost, Öl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>608692</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6296653</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gärdslösa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2005-07-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2005-07-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>kalkfuktäng</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13558-2025 artfynd.xlsx
+++ b/artfynd/A 13558-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6777289</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2992293</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2303068</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2457148</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3366866</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4797685</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1422,6 +1457,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5394863</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,8 +1568,23 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6104106</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>